--- a/data/output/evaluasi_16.xlsx
+++ b/data/output/evaluasi_16.xlsx
@@ -8,9 +8,23 @@
   </bookViews>
   <sheets>
     <sheet name="1600" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1609" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1603" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1604" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1604" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1606" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1601" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1603" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1605" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1607" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1602" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1673" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1610" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1672" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1611" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1613" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="1671" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="1612" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="1608" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="1609" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="1674" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,20 +488,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.44702130564207</v>
+        <v>1705.171678329046</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -506,7 +520,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-9.403925949681533</v>
+        <v>-12.17324383161278</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -515,7 +529,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -530,20 +544,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-14.27733056352122</v>
+        <v>-12.1390938445669</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -558,20 +572,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-14.03155647744767</v>
+        <v>-1407.612142860706</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -586,20 +600,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9639029438293614</v>
+        <v>7.505055387881487</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -614,20 +628,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.457983739822754</v>
+        <v>23.16234088910018</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -642,20 +656,2422 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5990336097505042</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>3.928669755944167</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D9" t="n">
+        <v>3.957140128224431</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.47390826876118</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.737572557988126</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-6.195725464446874</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-37.39326126611454</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.131170438722311</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.443570489225237</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q1-25 vs y-on-y_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.095895803127512</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q2-25 vs y-on-y_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4.447539646797854</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3.885257778781694</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25 vs y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4.293499419321078</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.40217853941449</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.833456919448168</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-4.655222712724647</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.158458196668741</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2277762793630056</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.831039162881761</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4.443570489225237</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q1-25 vs c-to-c_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4.266070683766611</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q2-25 vs c-to-c_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>4.32865984467525</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25 vs c-to-c_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3.885257778781694</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25 vs c-to-c_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2.40217853941449</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2277762793630056</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>16</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1.535792022894493</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>16</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.912125311493051</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.704781260873544</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q1-25 vs implisit_q-to-q_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.517769319432413</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q2-25 vs implisit_q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>16</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.1441202097819525</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25 vs implisit_q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>16</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.9232012597320226</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>16</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1.430212835293238</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>16</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-1.652467635897163</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>16</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.04196482221396412</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>16</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4.557175915287835</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q2-25 vs implisit_y-on-y_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>16</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>6.062054257141942</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1.779282131604524</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>16</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4.44394336815483</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3.737473833240231</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>16</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2.520469632993651</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25 vs implisit_y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.090526896831466</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.491574726614742</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.230000000000003</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3741692345123163</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.7532703855403886</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.9844373563169859</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1053964470823634</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.370107730693631</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.945334947544581</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1946565851043077</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1082605013989875</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.440149795194955</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4352841612904162</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.803435050788585</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.285053345368759</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.914520882753369</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.55728305430569</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.800588543192971</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Palembang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3438237574266789</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.07195673554705925</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.7706028146387089</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.538201355287694</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.90332589524188</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.994044941434927</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.632715319522456</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.350437297597569</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.4633585595034215</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3846832995452199</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4543540305919799</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.96864848315946</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.074097253136707</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.399558452307833</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8.066828057650516</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -670,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,169 +3123,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Ogan Komering Ulu Timur</t>
+          <t>Kabupaten Lahat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-69469.93134969485</v>
+        <v>-6360.899370338768</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Ogan Komering Ulu Timur</t>
+          <t>Kabupaten Lahat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.336744275134698</v>
+        <v>3.617376977463113</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Ogan Komering Ulu Timur</t>
+          <t>Kabupaten Lahat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.336744275134698</v>
+        <v>-1.937179966461229</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1609</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Ogan Komering Ulu Timur</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.9212501701349742</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1609</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Ogan Komering Ulu Timur</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-1.373719192770232</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1609</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Ogan Komering Ulu Timur</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.39215038340047</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -884,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,11 +3253,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Muara Enim</t>
+          <t>Kabupaten Musi Banyuasin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -934,16 +3266,632 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.27482224409369</v>
+        <v>-6.605874206788616</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q1-25_ril vs q-to-q_pdrb_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-3 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.452782385331262</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q2-25_ril vs q-to-q_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.9058900644612816</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q1-25_ril vs y-on-y_pdrb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.500582969647583</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q2-25_ril vs y-on-y_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.9058900644612816</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q1-25_ril vs c-to-c_pdrb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.217409061415701</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q2-25_ril vs c-to-c_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.596602175830411</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-3 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.446197414548298</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q2-25_ril vs implisit_q-to-q_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-3 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.400011959776142</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q1-25_ril vs implisit_y-on-y_pdrb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-3 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.24741087329489</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q2-25_ril vs implisit_y-on-y_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.452782385331262</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_q_pdrb_q2-25_ril vs sog_q_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.9058900644612816</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pdrb_q1-25_ril vs sog_y-on-y_pdrb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-5.500582969647583</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pdrb_q2-25_ril vs sog_y-on-y_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6.576031680455705</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.4203051771090366</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.589135013814002</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.4498565477723347</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.283930134640261</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1737276627049428</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.2325665389856168</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-3.696214061526967</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7.130007865870162</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.936661051407327</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -958,7 +3906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,11 +3943,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lahat</t>
+          <t>Kabupaten Ogan Komering Ulu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1008,16 +3956,1086 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3422794746110511</v>
+        <v>11.97268389783486</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.534971448661214</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25_ril vs implisit_q-to-q_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.99366984239036</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.104961016956066</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.410836905634096</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.03804240255395</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.7877595871471864</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.529491600074781</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5746689191945663</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6894269259942591</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.09233013225118</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.3013761721194314</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4190089540338976</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.295941448352768</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.566355399634522</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.103158737171206</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.58181342430968</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.315354143009823</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.195647600184957</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3945028614667284</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.94116960454484</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.198708257863849</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1546882888359221</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.684214230421443</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.110878684610509</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.579321624717441</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1149545846017262</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2266257015889992</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.04778938987791559</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.109379385398501</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.193340643449907</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_16.xlsx
+++ b/data/output/evaluasi_16.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
